--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:J57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2545,6 +2545,44 @@
       </c>
       <c r="F56" t="n">
         <v>77083.671875</v>
+      </c>
+      <c r="G56" t="n">
+        <v>77201.421875</v>
+      </c>
+      <c r="H56" t="n">
+        <v>117.75</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.1525230975546718</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.1749878258928136</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-13 04:31:17</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6</v>
+      </c>
+      <c r="F57" t="n">
+        <v>77081</v>
       </c>
     </row>
   </sheetData>
@@ -2558,7 +2596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M56"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5949,6 +5987,24 @@
           <t>77179.007812,77160.367188,77222.601562,77116.078125,77237.648438,77083.671875</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>77339.796875,77363.968750,77105.429688,77266.421875,77176.070312,77201.421875</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>160.789063,203.601562,117.171874,150.343750,61.578126,117.750000</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>0.207900,0.263174,0.151963,0.194578,0.079789,0.152523</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>0.1749878258928136</v>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
           <t>77072.164062,77124.468750,76995.187500,77034.273438,77347.929688,76852.632812</t>
@@ -5962,6 +6018,49 @@
       <c r="M56" t="inlineStr">
         <is>
           <t>76554.351562,76448.539062,76510.773438,76318.664062,76410.054688,76198.226562</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-13 04:31:17</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>77081.039062,77042.773438,77048.804688,77017.289062,77132.609375,77081.000000</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>76935.328125,77059.875000,76892.593750,76985.015625,77221.218750,76776.468750</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>76335.539062,76129.390625,76083.617188,76005.570312,76108.000000,75920.781250</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>76568.101562,76455.492188,76504.820312,76414.210938,76530.328125,76451.046875</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J57"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2583,6 +2583,44 @@
       </c>
       <c r="F57" t="n">
         <v>77081</v>
+      </c>
+      <c r="G57" t="n">
+        <v>77556.4375</v>
+      </c>
+      <c r="H57" t="n">
+        <v>475.4375</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.613021323987451</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.3702000976002833</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-14 04:37:38</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6</v>
+      </c>
+      <c r="F58" t="n">
+        <v>77270.0546875</v>
       </c>
     </row>
   </sheetData>
@@ -2596,7 +2634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6048,6 +6086,24 @@
           <t>77081.039062,77042.773438,77048.804688,77017.289062,77132.609375,77081.000000</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>76759.132812,77105.273438,77253.718750,76799.851562,77566.500000,77556.437500</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>321.906249,62.499999,204.914062,217.437499,433.890625,475.437500</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>0.419372,0.081058,0.265248,0.283122,0.559379,0.613021</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>0.3702000976002833</v>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
           <t>76935.328125,77059.875000,76892.593750,76985.015625,77221.218750,76776.468750</t>
@@ -6061,6 +6117,49 @@
       <c r="M57" t="inlineStr">
         <is>
           <t>76568.101562,76455.492188,76504.820312,76414.210938,76530.328125,76451.046875</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-14 04:37:38</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>77427.835938,77282.914062,77248.765625,77126.148438,77400.484375,77270.054688</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>77393.554688,77183.929688,77096.593750,76912.500000,77355.539062,77002.570312</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>76615.601562,76184.875000,76056.421875,75880.117188,76226.593750,75887.953125</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>76872.054688,76668.210938,76666.257812,76544.125000,76854.765625,76668.390625</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2621,6 +2621,44 @@
       </c>
       <c r="F58" t="n">
         <v>77270.0546875</v>
+      </c>
+      <c r="G58" t="n">
+        <v>77526.8203125</v>
+      </c>
+      <c r="H58" t="n">
+        <v>256.765625</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.3311958673979056</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1.03255793041672</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-15 04:38:06</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6</v>
+      </c>
+      <c r="F59" t="n">
+        <v>77056.328125</v>
       </c>
     </row>
   </sheetData>
@@ -2634,7 +2672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6147,6 +6185,24 @@
           <t>77427.835938,77282.914062,77248.765625,77126.148438,77400.484375,77270.054688</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>77736.421875,78552.437500,78973.117188,78192.453125,77636.406250,77526.820312</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>308.585937,1269.523438,1724.351562,1066.304687,235.921875,256.765624</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>0.396964,1.616148,2.183467,1.363693,0.303880,0.331196</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>1.03255793041672</v>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
           <t>77393.554688,77183.929688,77096.593750,76912.500000,77355.539062,77002.570312</t>
@@ -6160,6 +6216,49 @@
       <c r="M58" t="inlineStr">
         <is>
           <t>76872.054688,76668.210938,76666.257812,76544.125000,76854.765625,76668.390625</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-15 04:38:06</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>77367.781250,77258.679688,77101.640625,76977.898438,77001.851562,77056.328125</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>77183.382812,76929.632812,77137.125000,76975.718750,76945.695312,76659.656250</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>76697.335938,76314.023438,75965.984375,75530.710938,75555.867188,75123.796875</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>76871.781250,76839.265625,76479.414062,76282.773438,76235.500000,76117.609375</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2659,6 +2659,44 @@
       </c>
       <c r="F59" t="n">
         <v>77056.328125</v>
+      </c>
+      <c r="G59" t="n">
+        <v>75805.8984375</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1250.4296875</v>
+      </c>
+      <c r="I59" t="n">
+        <v>1.649515028874629</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1.345123846411927</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-16 04:33:21</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6</v>
+      </c>
+      <c r="F60" t="n">
+        <v>75715.2265625</v>
       </c>
     </row>
   </sheetData>
@@ -2672,7 +2710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6246,6 +6284,24 @@
           <t>77367.781250,77258.679688,77101.640625,76977.898438,77001.851562,77056.328125</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>76895.187500,76467.992188,76124.687500,75584.179688,75755.421875,75805.898438</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>472.593750,790.687501,976.953125,1393.718751,1246.429687,1250.429688</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>0.614595,1.034011,1.283359,1.843929,1.645334,1.649515</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>1.345123846411927</v>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
           <t>77183.382812,76929.632812,77137.125000,76975.718750,76945.695312,76659.656250</t>
@@ -6259,6 +6315,49 @@
       <c r="M59" t="inlineStr">
         <is>
           <t>76871.781250,76839.265625,76479.414062,76282.773438,76235.500000,76117.609375</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-16 04:33:21</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>75778.750000,75749.875000,75709.640625,75664.187500,75710.812500,75715.226562</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>75692.875000,75783.273438,75573.460938,75838.835938,75798.171875,75635.937500</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>75147.726562,74889.210938,74663.781250,74417.257812,74391.820312,74128.039062</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>75393.937500,75298.445312,75130.101562,74975.703125,74942.726562,74852.523438</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2697,6 +2697,44 @@
       </c>
       <c r="F60" t="n">
         <v>75715.2265625</v>
+      </c>
+      <c r="G60" t="n">
+        <v>76208.390625</v>
+      </c>
+      <c r="H60" t="n">
+        <v>493.1640625</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.6471256753429177</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.5142331129252736</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-17 04:38:45</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6</v>
+      </c>
+      <c r="F61" t="n">
+        <v>76050.4921875</v>
       </c>
     </row>
   </sheetData>
@@ -2710,7 +2748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6345,6 +6383,24 @@
           <t>75778.750000,75749.875000,75709.640625,75664.187500,75710.812500,75715.226562</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>76182.140625,75729.312500,76010.210938,76143.960938,76364.562500,76208.390625</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>403.390625,20.562500,300.570312,479.773438,653.750000,493.164063</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>0.529508,0.027153,0.395434,0.630087,0.856091,0.647126</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>0.5142331129252736</v>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
           <t>75692.875000,75783.273438,75573.460938,75838.835938,75798.171875,75635.937500</t>
@@ -6358,6 +6414,49 @@
       <c r="M60" t="inlineStr">
         <is>
           <t>75393.937500,75298.445312,75130.101562,74975.703125,74942.726562,74852.523438</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-17 04:38:45</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>76166.179688,76097.093750,76045.718750,76044.117188,76067.859375,76050.492188</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>76237.601562,76111.343750,76101.328125,76204.703125,76074.335938,76017.000000</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>75781.828125,75440.898438,75265.187500,75007.828125,75038.796875,74814.343750</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>75901.421875,75759.585938,75595.953125,75506.351562,75435.390625,75366.140625</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2735,6 +2735,44 @@
       </c>
       <c r="F61" t="n">
         <v>76050.4921875</v>
+      </c>
+      <c r="G61" t="n">
+        <v>77237.5390625</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1187.046875</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1.536878167544219</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.8733218708927558</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:24:01</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6</v>
+      </c>
+      <c r="F62" t="n">
+        <v>77063.453125</v>
       </c>
     </row>
   </sheetData>
@@ -2748,7 +2786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6444,6 +6482,24 @@
           <t>76166.179688,76097.093750,76045.718750,76044.117188,76067.859375,76050.492188</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>76400.992188,76676.421875,76543.343750,76348.742188,77297.703125,77237.539062</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>234.812499,579.328125,497.625000,304.624999,1229.843750,1187.046874</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>0.307342,0.755549,0.650122,0.398992,1.591048,1.536878</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>0.8733218708927558</v>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
           <t>76237.601562,76111.343750,76101.328125,76204.703125,76074.335938,76017.000000</t>
@@ -6457,6 +6513,49 @@
       <c r="M61" t="inlineStr">
         <is>
           <t>75901.421875,75759.585938,75595.953125,75506.351562,75435.390625,75366.140625</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:24:01</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>77117.460938,77118.921875,77111.812500,77099.898438,77100.250000,77063.453125</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>77129.625000,77112.164062,77110.078125,77173.078125,77072.984375,76981.046875</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>76556.343750,76342.679688,76209.546875,76011.054688,75972.718750,75806.226562</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>76784.234375,76689.062500,76598.359375,76486.390625,76420.398438,76304.367188</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2773,6 +2773,44 @@
       </c>
       <c r="F62" t="n">
         <v>77063.453125</v>
+      </c>
+      <c r="G62" t="n">
+        <v>81103.96875</v>
+      </c>
+      <c r="H62" t="n">
+        <v>4040.515625</v>
+      </c>
+      <c r="I62" t="n">
+        <v>4.981896308249404</v>
+      </c>
+      <c r="J62" t="n">
+        <v>4.193287573232055</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-19 04:20:52</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6</v>
+      </c>
+      <c r="F63" t="n">
+        <v>80189.359375</v>
       </c>
     </row>
   </sheetData>
@@ -2786,7 +2824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M62"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6543,6 +6581,24 @@
           <t>77117.460938,77118.921875,77111.812500,77099.898438,77100.250000,77063.453125</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>77995.187500,80698.242188,81180.000000,80875.101562,81105.031250,81103.968750</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>877.726562,3579.320312,4068.187500,3775.203124,4004.781250,4040.515625</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1.125360,4.435438,5.011317,4.667942,4.937772,4.981896</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>4.193287573232055</v>
+      </c>
       <c r="K62" t="inlineStr">
         <is>
           <t>77129.625000,77112.164062,77110.078125,77173.078125,77072.984375,76981.046875</t>
@@ -6556,6 +6612,49 @@
       <c r="M62" t="inlineStr">
         <is>
           <t>76784.234375,76689.062500,76598.359375,76486.390625,76420.398438,76304.367188</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-19 04:20:52</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>81058.406250,80878.234375,80680.984375,80481.781250,80311.937500,80189.359375</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>80984.750000,80692.234375,80601.796875,80349.734375,80134.281250,79988.140625</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>80219.828125,79766.062500,79340.046875,78891.562500,78542.875000,78263.796875</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>80563.312500,80190.546875,79834.437500,79513.000000,79200.578125,78973.695312</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2811,6 +2811,44 @@
       </c>
       <c r="F63" t="n">
         <v>80189.359375</v>
+      </c>
+      <c r="G63" t="n">
+        <v>80443.78125</v>
+      </c>
+      <c r="H63" t="n">
+        <v>254.421875</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.3162728939970111</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.5659090519296021</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-20 04:39:59</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6</v>
+      </c>
+      <c r="F64" t="n">
+        <v>79892.25</v>
       </c>
     </row>
   </sheetData>
@@ -2824,7 +2862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6642,6 +6680,24 @@
           <t>81058.406250,80878.234375,80680.984375,80481.781250,80311.937500,80189.359375</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>81280.000000,81610.820312,81332.382812,81233.539062,80458.820312,80443.781250</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>221.593750,732.585938,651.398438,751.757812,146.882812,254.421875</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>0.272630,0.897658,0.800909,0.925428,0.182557,0.316273</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>0.5659090519296021</v>
+      </c>
       <c r="K63" t="inlineStr">
         <is>
           <t>80984.750000,80692.234375,80601.796875,80349.734375,80134.281250,79988.140625</t>
@@ -6655,6 +6711,49 @@
       <c r="M63" t="inlineStr">
         <is>
           <t>80563.312500,80190.546875,79834.437500,79513.000000,79200.578125,78973.695312</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-20 04:39:59</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>80395.007812,80261.718750,80150.804688,80063.031250,79957.093750,79892.250000</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>80294.515625,80170.929688,80058.773438,79912.226562,79841.203125,79742.523438</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>79659.460938,79333.773438,79001.421875,78726.929688,78462.328125,78259.984375</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>79960.906250,79672.875000,79419.250000,79232.882812,79019.539062,78858.750000</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2849,6 +2849,44 @@
       </c>
       <c r="F64" t="n">
         <v>79892.25</v>
+      </c>
+      <c r="G64" t="n">
+        <v>81350.03125</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1457.78125</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1.791986097116588</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1.165484455411327</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-21 04:37:50</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6</v>
+      </c>
+      <c r="F65" t="n">
+        <v>81095.125</v>
       </c>
     </row>
   </sheetData>
@@ -2862,7 +2900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6741,6 +6779,24 @@
           <t>80395.007812,80261.718750,80150.804688,80063.031250,79957.093750,79892.250000</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>80442.976562,80874.210938,81162.437500,81159.523438,81411.500000,81350.031250</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>47.968751,612.492188,1011.632812,1096.492188,1454.406250,1457.781250</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>0.059631,0.757339,1.246430,1.351033,1.786487,1.791986</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>1.165484455411327</v>
+      </c>
       <c r="K64" t="inlineStr">
         <is>
           <t>80294.515625,80170.929688,80058.773438,79912.226562,79841.203125,79742.523438</t>
@@ -6754,6 +6810,49 @@
       <c r="M64" t="inlineStr">
         <is>
           <t>79960.906250,79672.875000,79419.250000,79232.882812,79019.539062,78858.750000</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-21 04:37:50</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>81323.359375,81275.859375,81222.054688,81170.078125,81120.414062,81095.125000</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>81178.984375,81141.671875,81079.203125,81017.523438,80892.039062,80805.781250</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>80710.304688,80502.359375,80237.484375,79998.312500,79771.734375,79612.523438</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>80988.132812,80825.375000,80635.523438,80498.828125,80318.976562,80204.171875</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2887,6 +2887,44 @@
       </c>
       <c r="F65" t="n">
         <v>81095.125</v>
+      </c>
+      <c r="G65" t="n">
+        <v>85470.3984375</v>
+      </c>
+      <c r="H65" t="n">
+        <v>4375.2734375</v>
+      </c>
+      <c r="I65" t="n">
+        <v>5.119051177349322</v>
+      </c>
+      <c r="J65" t="n">
+        <v>5.398563671134787</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-22 04:33:51</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6</v>
+      </c>
+      <c r="F66" t="n">
+        <v>84196.140625</v>
       </c>
     </row>
   </sheetData>
@@ -2900,7 +2938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M65"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6840,6 +6878,24 @@
           <t>81323.359375,81275.859375,81222.054688,81170.078125,81120.414062,81095.125000</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>84863.609375,85933.156250,86501.828125,86591.750000,85675.000000,85470.398438</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>3540.250000,4657.296875,5279.773437,5421.671875,4554.585938,4375.273438</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>4.171694,5.419674,6.103655,6.261188,5.316120,5.119051</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>5.398563671134787</v>
+      </c>
       <c r="K65" t="inlineStr">
         <is>
           <t>81178.984375,81141.671875,81079.203125,81017.523438,80892.039062,80805.781250</t>
@@ -6853,6 +6909,49 @@
       <c r="M65" t="inlineStr">
         <is>
           <t>80988.132812,80825.375000,80635.523438,80498.828125,80318.976562,80204.171875</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-22 04:33:51</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>85067.546875,84889.164062,84726.281250,84487.132812,84364.554688,84196.140625</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>84893.671875,84686.109375,84579.898438,84284.929688,84132.789062,83890.210938</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>83997.398438,83486.312500,82970.601562,82415.304688,81993.804688,81570.187500</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>84431.296875,84042.250000,83627.640625,83242.390625,82896.390625,82551.171875</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2925,6 +2925,44 @@
       </c>
       <c r="F66" t="n">
         <v>84196.140625</v>
+      </c>
+      <c r="G66" t="n">
+        <v>87026.671875</v>
+      </c>
+      <c r="H66" t="n">
+        <v>2830.53125</v>
+      </c>
+      <c r="I66" t="n">
+        <v>3.252487069786615</v>
+      </c>
+      <c r="J66" t="n">
+        <v>2.08284198264799</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-23 04:30:13</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6</v>
+      </c>
+      <c r="F67" t="n">
+        <v>86899.3203125</v>
       </c>
     </row>
   </sheetData>
@@ -2938,7 +2976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6939,6 +6977,24 @@
           <t>85067.546875,84889.164062,84726.281250,84487.132812,84364.554688,84196.140625</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>85969.070312,86418.453125,86236.921875,86198.046875,86696.406250,87026.671875</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>901.523438,1529.289063,1510.640625,1710.914063,2331.851562,2830.531250</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1.048660,1.769633,1.751733,1.984864,2.689675,3.252487</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>2.08284198264799</v>
+      </c>
       <c r="K66" t="inlineStr">
         <is>
           <t>84893.671875,84686.109375,84579.898438,84284.929688,84132.789062,83890.210938</t>
@@ -6952,6 +7008,49 @@
       <c r="M66" t="inlineStr">
         <is>
           <t>84431.296875,84042.250000,83627.640625,83242.390625,82896.390625,82551.171875</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-23 04:30:13</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>87080.367188,87024.625000,87001.046875,86940.695312,86885.648438,86899.320312</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>86913.859375,86752.921875,86859.171875,86725.195312,86456.343750,86485.718750</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>85907.421875,85606.015625,85254.851562,84913.367188,84549.421875,84341.734375</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>86468.375000,86224.117188,85979.875000,85797.281250,85546.406250,85376.843750</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2963,6 +2963,44 @@
       </c>
       <c r="F67" t="n">
         <v>86899.3203125</v>
+      </c>
+      <c r="G67" t="n">
+        <v>83867.21875</v>
+      </c>
+      <c r="H67" t="n">
+        <v>3032.1015625</v>
+      </c>
+      <c r="I67" t="n">
+        <v>3.615359621663858</v>
+      </c>
+      <c r="J67" t="n">
+        <v>3.070825911022973</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:27:27</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6</v>
+      </c>
+      <c r="F68" t="n">
+        <v>83321.796875</v>
       </c>
     </row>
   </sheetData>
@@ -2976,7 +3014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M67"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7038,6 +7076,24 @@
           <t>87080.367188,87024.625000,87001.046875,86940.695312,86885.648438,86899.320312</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>85632.039062,84001.882812,84509.820312,84369.007812,83928.156250,83867.218750</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>1448.328126,3022.742188,2491.226562,2571.687499,2957.492188,3032.101562</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1.691339,3.598422,2.947855,3.048142,3.523838,3.615360</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>3.070825911022973</v>
+      </c>
       <c r="K67" t="inlineStr">
         <is>
           <t>86913.859375,86752.921875,86859.171875,86725.195312,86456.343750,86485.718750</t>
@@ -7051,6 +7107,49 @@
       <c r="M67" t="inlineStr">
         <is>
           <t>86468.375000,86224.117188,85979.875000,85797.281250,85546.406250,85376.843750</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:27:27</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>83675.875000,83518.898438,83431.921875,83366.054688,83328.710938,83321.796875</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>83475.921875,83549.554688,83456.914062,83320.062500,83133.976562,83269.617188</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>82817.945312,82490.843750,82175.843750,81862.203125,81679.570312,81453.953125</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>83167.984375,82889.593750,82627.742188,82497.468750,82302.789062,82169.445312</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3001,6 +3001,44 @@
       </c>
       <c r="F68" t="n">
         <v>83321.796875</v>
+      </c>
+      <c r="G68" t="n">
+        <v>84183.6015625</v>
+      </c>
+      <c r="H68" t="n">
+        <v>861.8046875</v>
+      </c>
+      <c r="I68" t="n">
+        <v>1.023720382003584</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.9518348025413986</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-25 04:38:45</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6</v>
+      </c>
+      <c r="F69" t="n">
+        <v>83917.59375</v>
       </c>
     </row>
   </sheetData>
@@ -3014,7 +3052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M68"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7137,6 +7175,24 @@
           <t>83675.875000,83518.898438,83431.921875,83366.054688,83328.710938,83321.796875</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>83461.343750,84392.218750,84388.710938,84385.460938,84216.000000,84183.601562</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>214.531250,873.320312,956.789062,1019.406249,887.289062,861.804688</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>0.257043,1.034835,1.133788,1.208035,1.053587,1.023720</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>0.9518348025413986</v>
+      </c>
       <c r="K68" t="inlineStr">
         <is>
           <t>83475.921875,83549.554688,83456.914062,83320.062500,83133.976562,83269.617188</t>
@@ -7150,6 +7206,49 @@
       <c r="M68" t="inlineStr">
         <is>
           <t>83167.984375,82889.593750,82627.742188,82497.468750,82302.789062,82169.445312</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-25 04:38:45</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>84208.484375,84125.617188,84062.718750,83993.640625,83952.984375,83917.593750</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>84039.226562,84195.281250,84003.929688,83935.648438,83775.726562,83774.234375</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>83482.703125,83223.734375,82936.507812,82722.218750,82536.273438,82311.632812</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>83803.453125,83614.953125,83383.593750,83283.132812,83094.664062,82964.929688</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3039,6 +3039,44 @@
       </c>
       <c r="F69" t="n">
         <v>83917.59375</v>
+      </c>
+      <c r="G69" t="n">
+        <v>83930.5625</v>
+      </c>
+      <c r="H69" t="n">
+        <v>12.96875</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.01545176109119965</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.1769213675311611</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-26 04:42:34</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6</v>
+      </c>
+      <c r="F70" t="n">
+        <v>83619.078125</v>
       </c>
     </row>
   </sheetData>
@@ -3052,7 +3090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M69"/>
+  <dimension ref="A1:M70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7236,6 +7274,24 @@
           <t>84208.484375,84125.617188,84062.718750,83993.640625,83952.984375,83917.593750</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>84566.679688,83781.710938,84005.812500,84093.132812,83931.179688,83930.562500</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>358.195312,343.906251,56.906250,99.492188,21.804688,12.968750</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>0.423566,0.410479,0.067741,0.118312,0.025979,0.015452</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>0.1769213675311611</v>
+      </c>
       <c r="K69" t="inlineStr">
         <is>
           <t>84039.226562,84195.281250,84003.929688,83935.648438,83775.726562,83774.234375</t>
@@ -7249,6 +7305,49 @@
       <c r="M69" t="inlineStr">
         <is>
           <t>83803.453125,83614.953125,83383.593750,83283.132812,83094.664062,82964.929688</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-26 04:42:34</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>83857.406250,83817.023438,83797.203125,83729.148438,83637.742188,83619.078125</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>83790.953125,83920.015625,83780.625000,83759.718750,83547.554688,83559.781250</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>83030.039062,82844.632812,82632.914062,82451.335938,82197.468750,82046.046875</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>83372.367188,83236.429688,83051.007812,82957.648438,82742.382812,82659.117188</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3077,6 +3077,44 @@
       </c>
       <c r="F70" t="n">
         <v>83619.078125</v>
+      </c>
+      <c r="G70" t="n">
+        <v>84335.4765625</v>
+      </c>
+      <c r="H70" t="n">
+        <v>716.3984375</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.8494627251783962</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.5896822614384344</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-27 05:02:33</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6</v>
+      </c>
+      <c r="F71" t="n">
+        <v>84034.59375</v>
       </c>
     </row>
   </sheetData>
@@ -3090,7 +3128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M70"/>
+  <dimension ref="A1:M71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7335,6 +7373,24 @@
           <t>83857.406250,83817.023438,83797.203125,83729.148438,83637.742188,83619.078125</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>84161.007812,84146.859375,84000.250000,84421.437500,84375.312500,84335.476562</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>303.601562,329.835937,203.046875,692.289062,737.570312,716.398438</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>0.360739,0.391977,0.241722,0.820039,0.874154,0.849463</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>0.5896822614384344</v>
+      </c>
       <c r="K70" t="inlineStr">
         <is>
           <t>83790.953125,83920.015625,83780.625000,83759.718750,83547.554688,83559.781250</t>
@@ -7348,6 +7404,49 @@
       <c r="M70" t="inlineStr">
         <is>
           <t>83372.367188,83236.429688,83051.007812,82957.648438,82742.382812,82659.117188</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-27 05:02:33</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>84234.460938,84168.031250,84125.601562,84129.562500,84019.359375,84034.593750</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>84142.109375,84222.578125,84140.437500,84116.250000,84026.226562,83944.539062</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>83639.304688,83464.257812,83231.679688,83167.648438,82906.312500,82747.242188</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>83884.382812,83759.890625,83568.351562,83538.593750,83324.609375,83239.320312</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J71"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3115,6 +3115,44 @@
       </c>
       <c r="F71" t="n">
         <v>84034.59375</v>
+      </c>
+      <c r="G71" t="n">
+        <v>83360</v>
+      </c>
+      <c r="H71" t="n">
+        <v>674.59375</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.8092535388675625</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.6375833757634339</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-09-28 05:04:18</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6</v>
+      </c>
+      <c r="F72" t="n">
+        <v>83298.734375</v>
       </c>
     </row>
   </sheetData>
@@ -3128,7 +3166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:M72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7434,6 +7472,24 @@
           <t>84234.460938,84168.031250,84125.601562,84129.562500,84019.359375,84034.593750</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>84877.023438,84449.476562,84717.820312,84462.132812,83325.156250,83360.000000</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>642.562499,281.445312,592.218751,332.570312,694.203125,674.593750</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>0.757051,0.333271,0.699049,0.393751,0.833126,0.809254</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>0.6375833757634339</v>
+      </c>
       <c r="K71" t="inlineStr">
         <is>
           <t>84142.109375,84222.578125,84140.437500,84116.250000,84026.226562,83944.539062</t>
@@ -7447,6 +7503,49 @@
       <c r="M71" t="inlineStr">
         <is>
           <t>83884.382812,83759.890625,83568.351562,83538.593750,83324.609375,83239.320312</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-09-28 05:04:18</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>83347.351562,83263.890625,83225.468750,83244.617188,83270.546875,83298.734375</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>83295.828125,83342.226562,83237.640625,83290.648438,83252.781250,83219.492188</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>82591.031250,82362.812500,82130.640625,82041.898438,81865.421875,81721.757812</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>82879.031250,82674.593750,82507.156250,82489.242188,82374.757812,82284.890625</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3153,6 +3153,44 @@
       </c>
       <c r="F72" t="n">
         <v>83298.734375</v>
+      </c>
+      <c r="G72" t="n">
+        <v>83281.3203125</v>
+      </c>
+      <c r="H72" t="n">
+        <v>17.4140625</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.02090992606103803</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.1985561590177962</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-09-29 05:29:02</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6</v>
+      </c>
+      <c r="F73" t="n">
+        <v>83343.640625</v>
       </c>
     </row>
   </sheetData>
@@ -3166,7 +3204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M72"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7533,6 +7571,24 @@
           <t>83347.351562,83263.890625,83225.468750,83244.617188,83270.546875,83298.734375</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>83058.929688,83365.789062,83364.843750,83456.742188,83038.382812,83281.320312</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>288.421874,101.898438,139.375000,212.124999,232.164062,17.414062</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>0.347250,0.122231,0.167187,0.254174,0.279586,0.020910</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>0.1985561590177962</v>
+      </c>
       <c r="K72" t="inlineStr">
         <is>
           <t>83295.828125,83342.226562,83237.640625,83290.648438,83252.781250,83219.492188</t>
@@ -7546,6 +7602,49 @@
       <c r="M72" t="inlineStr">
         <is>
           <t>82879.031250,82674.593750,82507.156250,82489.242188,82374.757812,82284.890625</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-09-29 05:29:02</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>83262.984375,83265.828125,83296.156250,83317.031250,83354.859375,83343.640625</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>83209.796875,83328.500000,83291.890625,83335.171875,83413.593750,83292.515625</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>82750.734375,82632.265625,82472.484375,82398.781250,82268.593750,82111.343750</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>82941.156250,82858.984375,82750.125000,82746.609375,82664.171875,82582.062500</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3191,6 +3191,44 @@
       </c>
       <c r="F73" t="n">
         <v>83343.640625</v>
+      </c>
+      <c r="G73" t="n">
+        <v>83150</v>
+      </c>
+      <c r="H73" t="n">
+        <v>193.640625</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.2328810883944679</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.425209173584896</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-09-30 05:16:36</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6</v>
+      </c>
+      <c r="F74" t="n">
+        <v>82916.390625</v>
       </c>
     </row>
   </sheetData>
@@ -3204,7 +3242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M73"/>
+  <dimension ref="A1:M74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7632,6 +7670,24 @@
           <t>83262.984375,83265.828125,83296.156250,83317.031250,83354.859375,83343.640625</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>84324.031250,83041.390625,83549.007812,83638.406250,83269.156250,83150.000000</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>1061.046875,224.437500,252.851562,321.375000,85.703125,193.640625</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1.258297,0.270272,0.302639,0.384243,0.102923,0.232881</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>0.425209173584896</v>
+      </c>
       <c r="K73" t="inlineStr">
         <is>
           <t>83209.796875,83328.500000,83291.890625,83335.171875,83413.593750,83292.515625</t>
@@ -7645,6 +7701,49 @@
       <c r="M73" t="inlineStr">
         <is>
           <t>82941.156250,82858.984375,82750.125000,82746.609375,82664.171875,82582.062500</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-09-30 05:16:36</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>83075.531250,83050.234375,83059.007812,83011.804688,82966.335938,82916.390625</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>83077.046875,83077.921875,83072.687500,83094.546875,83016.710938,82980.882812</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>82508.726562,82369.148438,82223.726562,82074.507812,81877.070312,81710.367188</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>82715.507812,82604.257812,82481.203125,82419.640625,82255.093750,82146.546875</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:J75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3229,6 +3229,44 @@
       </c>
       <c r="F74" t="n">
         <v>82916.390625</v>
+      </c>
+      <c r="G74" t="n">
+        <v>84208.9921875</v>
+      </c>
+      <c r="H74" t="n">
+        <v>1292.6015625</v>
+      </c>
+      <c r="I74" t="n">
+        <v>1.534992319611057</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.9729158559845476</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-10-01 05:31:47</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6</v>
+      </c>
+      <c r="F75" t="n">
+        <v>83798.4375</v>
       </c>
     </row>
   </sheetData>
@@ -3242,7 +3280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7731,6 +7769,24 @@
           <t>83075.531250,83050.234375,83059.007812,83011.804688,82966.335938,82916.390625</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>83879.007812,84078.968750,83558.976562,83556.148438,83695.539062,84208.992188</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>803.476562,1028.734375,499.968751,544.343749,729.203124,1292.601562</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>0.957899,1.223534,0.598342,0.651471,0.871257,1.534992</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>0.9729158559845476</v>
+      </c>
       <c r="K74" t="inlineStr">
         <is>
           <t>83077.046875,83077.921875,83072.687500,83094.546875,83016.710938,82980.882812</t>
@@ -7744,6 +7800,49 @@
       <c r="M74" t="inlineStr">
         <is>
           <t>82715.507812,82604.257812,82481.203125,82419.640625,82255.093750,82146.546875</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-10-01 05:31:47</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>84050.429688,84025.031250,83968.992188,83939.578125,83871.226562,83798.437500</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>84066.054688,84001.898438,83945.367188,83915.031250,83832.523438,83800.773438</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>83458.796875,83317.820312,83107.812500,83037.765625,82852.070312,82702.695312</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>83668.984375,83569.070312,83401.835938,83380.468750,83199.460938,83106.562500</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3267,6 +3267,44 @@
       </c>
       <c r="F75" t="n">
         <v>83798.4375</v>
+      </c>
+      <c r="G75" t="n">
+        <v>86467.0625</v>
+      </c>
+      <c r="H75" t="n">
+        <v>2668.625</v>
+      </c>
+      <c r="I75" t="n">
+        <v>3.086290805819846</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1.195111339217089</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-10-02 05:19:23</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6</v>
+      </c>
+      <c r="F76" t="n">
+        <v>85742.2265625</v>
       </c>
     </row>
   </sheetData>
@@ -3280,7 +3318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M75"/>
+  <dimension ref="A1:M76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7830,6 +7868,24 @@
           <t>84050.429688,84025.031250,83968.992188,83939.578125,83871.226562,83798.437500</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>83882.023438,84130.062500,84644.929688,84848.726562,85485.812500,86467.062500</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>168.406251,105.031250,675.937499,909.148438,1614.585938,2668.625000</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>0.200766,0.124844,0.798556,1.071493,1.888718,3.086291</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>1.195111339217089</v>
+      </c>
       <c r="K75" t="inlineStr">
         <is>
           <t>84066.054688,84001.898438,83945.367188,83915.031250,83832.523438,83800.773438</t>
@@ -7843,6 +7899,49 @@
       <c r="M75" t="inlineStr">
         <is>
           <t>83668.984375,83569.070312,83401.835938,83380.468750,83199.460938,83106.562500</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-10-02 05:19:23</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>86292.484375,86122.773438,85896.281250,85826.984375,85776.140625,85742.226562</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>86315.039062,86098.109375,85920.695312,85834.546875,85806.507812,85745.226562</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>84915.500000,84553.593750,84144.679688,83971.070312,83814.609375,83654.265625</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>85409.054688,85132.968750,84782.968750,84651.617188,84472.664062,84385.789062</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:J77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3305,6 +3305,44 @@
       </c>
       <c r="F76" t="n">
         <v>85742.2265625</v>
+      </c>
+      <c r="G76" t="n">
+        <v>84538.0078125</v>
+      </c>
+      <c r="H76" t="n">
+        <v>1204.21875</v>
+      </c>
+      <c r="I76" t="n">
+        <v>1.424470224884979</v>
+      </c>
+      <c r="J76" t="n">
+        <v>1.211645728706755</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-10-03 05:02:12</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6</v>
+      </c>
+      <c r="F77" t="n">
+        <v>84410.703125</v>
       </c>
     </row>
   </sheetData>
@@ -3318,7 +3356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M76"/>
+  <dimension ref="A1:M77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7929,6 +7967,24 @@
           <t>86292.484375,86122.773438,85896.281250,85826.984375,85776.140625,85742.226562</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>86412.210938,85316.351562,84291.492188,84504.882812,84681.000000,84538.007812</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>119.726562,806.421876,1604.789062,1322.101562,1095.140625,1204.218749</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>0.138553,0.945214,1.903857,1.564527,1.293254,1.424470</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>1.211645728706755</v>
+      </c>
       <c r="K76" t="inlineStr">
         <is>
           <t>86315.039062,86098.109375,85920.695312,85834.546875,85806.507812,85745.226562</t>
@@ -7942,6 +7998,49 @@
       <c r="M76" t="inlineStr">
         <is>
           <t>85409.054688,85132.968750,84782.968750,84651.617188,84472.664062,84385.789062</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-10-03 05:02:12</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>84487.742188,84467.250000,84383.703125,84396.398438,84391.132812,84410.703125</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>84566.945312,84549.320312,84471.203125,84458.804688,84426.109375,84385.335938</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>83735.757812,83651.187500,83460.898438,83440.250000,83333.210938,83324.070312</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>83990.703125,83937.687500,83786.250000,83785.125000,83734.906250,83713.398438</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:J78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3343,6 +3343,44 @@
       </c>
       <c r="F77" t="n">
         <v>84410.703125</v>
+      </c>
+      <c r="G77" t="n">
+        <v>84854.546875</v>
+      </c>
+      <c r="H77" t="n">
+        <v>443.84375</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.5230641920153439</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.4411986226819498</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-10-04 05:34:34</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6</v>
+      </c>
+      <c r="F78" t="n">
+        <v>84814.09375</v>
       </c>
     </row>
   </sheetData>
@@ -3356,7 +3394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M77"/>
+  <dimension ref="A1:M78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8028,6 +8066,24 @@
           <t>84487.742188,84467.250000,84383.703125,84396.398438,84391.132812,84410.703125</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>84661.851562,84862.156250,84836.992188,84742.218750,84824.359375,84854.546875</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>174.109374,394.906250,453.289062,345.820312,433.226563,443.843750</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>0.205653,0.465350,0.534306,0.408085,0.510734,0.523064</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>0.4411986226819498</v>
+      </c>
       <c r="K77" t="inlineStr">
         <is>
           <t>84566.945312,84549.320312,84471.203125,84458.804688,84426.109375,84385.335938</t>
@@ -8041,6 +8097,49 @@
       <c r="M77" t="inlineStr">
         <is>
           <t>83990.703125,83937.687500,83786.250000,83785.125000,83734.906250,83713.398438</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-10-04 05:34:34</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>84911.250000,84852.843750,84826.156250,84805.218750,84803.125000,84814.093750</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>84934.921875,84862.500000,84875.937500,84807.687500,84768.312500,84735.109375</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>84281.125000,84135.921875,83994.796875,83931.890625,83832.390625,83754.953125</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>84516.015625,84408.656250,84317.156250,84262.218750,84191.437500,84155.484375</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3381,6 +3381,44 @@
       </c>
       <c r="F78" t="n">
         <v>84814.09375</v>
+      </c>
+      <c r="G78" t="n">
+        <v>85445.171875</v>
+      </c>
+      <c r="H78" t="n">
+        <v>631.078125</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.7385766932779079</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.9628485337283511</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-10-05 05:18:20</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6</v>
+      </c>
+      <c r="F79" t="n">
+        <v>85315.0859375</v>
       </c>
     </row>
   </sheetData>
@@ -3394,7 +3432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M78"/>
+  <dimension ref="A1:M79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8127,6 +8165,24 @@
           <t>84911.250000,84852.843750,84826.156250,84805.218750,84803.125000,84814.093750</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>85304.171875,85244.976562,85417.468750,86512.976562,86052.296875,85445.171875</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>392.921875,392.132812,591.312500,1707.757812,1249.171875,631.078125</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>0.460613,0.460007,0.692262,1.973990,1.451643,0.738577</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>0.9628485337283511</v>
+      </c>
       <c r="K78" t="inlineStr">
         <is>
           <t>84934.921875,84862.500000,84875.937500,84807.687500,84768.312500,84735.109375</t>
@@ -8140,6 +8196,49 @@
       <c r="M78" t="inlineStr">
         <is>
           <t>84516.015625,84408.656250,84317.156250,84262.218750,84191.437500,84155.484375</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-10-05 05:18:20</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>85408.796875,85370.671875,85304.921875,85292.585938,85306.398438,85315.085938</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>85425.609375,85321.789062,85398.109375,85235.750000,85281.765625,85215.257812</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>84739.554688,84606.273438,84398.617188,84337.000000,84286.179688,84208.812500</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>84973.625000,84895.718750,84742.757812,84696.585938,84665.867188,84614.023438</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3419,6 +3419,44 @@
       </c>
       <c r="F79" t="n">
         <v>85315.0859375</v>
+      </c>
+      <c r="G79" t="n">
+        <v>85388.4609375</v>
+      </c>
+      <c r="H79" t="n">
+        <v>73.375</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.08593081453207918</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.3935743292350454</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:02:27</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6</v>
+      </c>
+      <c r="F80" t="n">
+        <v>85140.734375</v>
       </c>
     </row>
   </sheetData>
@@ -3432,7 +3470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M79"/>
+  <dimension ref="A1:M80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8226,6 +8264,24 @@
           <t>85408.796875,85370.671875,85304.921875,85292.585938,85306.398438,85315.085938</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>86197.921875,85251.546875,85724.546875,85748.953125,85476.140625,85388.460938</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>789.125000,119.125000,419.625000,456.367187,169.742187,73.374999</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>0.915480,0.139734,0.489504,0.532213,0.198584,0.085931</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>0.3935743292350454</v>
+      </c>
       <c r="K79" t="inlineStr">
         <is>
           <t>85425.609375,85321.789062,85398.109375,85235.750000,85281.765625,85215.257812</t>
@@ -8239,6 +8295,49 @@
       <c r="M79" t="inlineStr">
         <is>
           <t>84973.625000,84895.718750,84742.757812,84696.585938,84665.867188,84614.023438</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:02:27</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>85344.023438,85353.539062,85276.562500,85189.695312,85181.085938,85140.734375</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>85357.085938,85310.851562,85330.070312,85126.921875,85084.757812,84967.195312</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>84697.335938,84533.523438,84305.437500,84126.000000,84015.460938,83914.031250</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>84913.718750,84833.757812,84646.125000,84496.445312,84407.429688,84331.320312</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J80"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3457,6 +3457,44 @@
       </c>
       <c r="F80" t="n">
         <v>85140.734375</v>
+      </c>
+      <c r="G80" t="n">
+        <v>84171.6171875</v>
+      </c>
+      <c r="H80" t="n">
+        <v>969.1171875</v>
+      </c>
+      <c r="I80" t="n">
+        <v>1.151358640693813</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.7780370928509427</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-10-07 05:37:39</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6</v>
+      </c>
+      <c r="F81" t="n">
+        <v>84460.75</v>
       </c>
     </row>
   </sheetData>
@@ -3470,7 +3508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M80"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8325,6 +8363,24 @@
           <t>85344.023438,85353.539062,85276.562500,85189.695312,85181.085938,85140.734375</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>86236.187500,85710.000000,85610.000000,85547.773438,84122.523438,84171.617188</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>892.164062,356.460938,333.437500,358.078126,1058.562501,969.117188</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1.034559,0.415892,0.389484,0.418571,1.258358,1.151359</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>0.7780370928509427</v>
+      </c>
       <c r="K80" t="inlineStr">
         <is>
           <t>85357.085938,85310.851562,85330.070312,85126.921875,85084.757812,84967.195312</t>
@@ -8338,6 +8394,49 @@
       <c r="M80" t="inlineStr">
         <is>
           <t>84913.718750,84833.757812,84646.125000,84496.445312,84407.429688,84331.320312</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-10-07 05:37:39</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>84343.390625,84336.812500,84378.039062,84355.421875,84413.507812,84460.750000</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>84361.546875,84350.031250,84376.742188,84452.015625,84381.304688,84324.367188</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>83549.429688,83395.117188,83299.359375,83206.164062,83105.437500,83082.242188</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>83823.304688,83714.671875,83670.671875,83614.937500,83565.578125,83540.046875</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:J82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3495,6 +3495,44 @@
       </c>
       <c r="F81" t="n">
         <v>84460.75</v>
+      </c>
+      <c r="G81" t="n">
+        <v>82844.3203125</v>
+      </c>
+      <c r="H81" t="n">
+        <v>1616.4296875</v>
+      </c>
+      <c r="I81" t="n">
+        <v>1.951165368250483</v>
+      </c>
+      <c r="J81" t="n">
+        <v>1.394617041929449</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-10-08 05:45:53</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6</v>
+      </c>
+      <c r="F82" t="n">
+        <v>82603.5078125</v>
       </c>
     </row>
   </sheetData>
@@ -3508,7 +3546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:M82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8424,6 +8462,24 @@
           <t>84343.390625,84336.812500,84378.039062,84355.421875,84413.507812,84460.750000</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>83709.531250,83417.398438,83392.039062,83275.062500,82695.562500,82844.320312</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>633.859375,919.414062,985.999999,1080.359375,1717.945312,1616.429688</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>0.757213,1.102185,1.182367,1.297338,2.077433,1.951165</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>1.394617041929449</v>
+      </c>
       <c r="K81" t="inlineStr">
         <is>
           <t>84361.546875,84350.031250,84376.742188,84452.015625,84381.304688,84324.367188</t>
@@ -8437,6 +8493,49 @@
       <c r="M81" t="inlineStr">
         <is>
           <t>83823.304688,83714.671875,83670.671875,83614.937500,83565.578125,83540.046875</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-10-08 05:45:53</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>82844.882812,82774.679688,82757.429688,82724.914062,82675.250000,82603.507812</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>82865.289062,82912.859375,82753.023438,82820.234375,82761.953125,82596.937500</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>82094.273438,81889.453125,81737.351562,81610.046875,81449.976562,81288.460938</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>82334.921875,82173.789062,82061.882812,81986.921875,81881.921875,81734.929688</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J82"/>
+  <dimension ref="A1:J83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3533,6 +3533,44 @@
       </c>
       <c r="F82" t="n">
         <v>82603.5078125</v>
+      </c>
+      <c r="G82" t="n">
+        <v>82304.2734375</v>
+      </c>
+      <c r="H82" t="n">
+        <v>299.234375</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0.3635708845996093</v>
+      </c>
+      <c r="J82" t="n">
+        <v>1.001152483281679</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-10-09 05:49:57</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6</v>
+      </c>
+      <c r="F83" t="n">
+        <v>82165.4375</v>
       </c>
     </row>
   </sheetData>
@@ -3546,7 +3584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M82"/>
+  <dimension ref="A1:M83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8523,6 +8561,24 @@
           <t>82844.882812,82774.679688,82757.429688,82724.914062,82675.250000,82603.507812</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>82429.117188,80989.343750,81704.578125,81692.789062,82360.210938,82304.273438</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>415.765624,1785.335938,1052.851563,1032.124999,315.039062,299.234374</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>0.504392,2.204408,1.288608,1.263422,0.382514,0.363571</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>1.001152483281679</v>
+      </c>
       <c r="K82" t="inlineStr">
         <is>
           <t>82865.289062,82912.859375,82753.023438,82820.234375,82761.953125,82596.937500</t>
@@ -8536,6 +8592,49 @@
       <c r="M82" t="inlineStr">
         <is>
           <t>82334.921875,82173.789062,82061.882812,81986.921875,81881.921875,81734.929688</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-10-09 05:49:57</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>82260.593750,82252.195312,82198.148438,82168.054688,82212.765625,82165.437500</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>82202.000000,82389.890625,82134.242188,82233.750000,82214.570312,82206.992188</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>81259.617188,81091.906250,80849.242188,80702.578125,80573.406250,80434.187500</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>81645.367188,81524.703125,81337.875000,81233.578125,81166.507812,81081.531250</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J83"/>
+  <dimension ref="A1:J84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3571,6 +3571,44 @@
       </c>
       <c r="F83" t="n">
         <v>82165.4375</v>
+      </c>
+      <c r="G83" t="n">
+        <v>82650</v>
+      </c>
+      <c r="H83" t="n">
+        <v>484.5625</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.5862825166364186</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0.5417196310546709</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-10-10 05:33:20</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6</v>
+      </c>
+      <c r="F84" t="n">
+        <v>82490.03125</v>
       </c>
     </row>
   </sheetData>
@@ -3584,7 +3622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M83"/>
+  <dimension ref="A1:M84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8622,6 +8660,24 @@
           <t>82260.593750,82252.195312,82198.148438,82168.054688,82212.765625,82165.437500</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>83175.109375,82807.476562,82251.968750,82544.710938,82519.921875,82650.000000</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>914.515625,555.281251,53.820312,376.656249,307.156250,484.562500</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1.099506,0.670569,0.065433,0.456306,0.372221,0.586283</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>0.5417196310546709</v>
+      </c>
       <c r="K83" t="inlineStr">
         <is>
           <t>82202.000000,82389.890625,82134.242188,82233.750000,82214.570312,82206.992188</t>
@@ -8635,6 +8691,49 @@
       <c r="M83" t="inlineStr">
         <is>
           <t>81645.367188,81524.703125,81337.875000,81233.578125,81166.507812,81081.531250</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-10-10 05:33:20</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>82666.835938,82648.687500,82644.046875,82577.320312,82590.945312,82490.031250</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>82652.382812,82782.132812,82624.257812,82615.773438,82620.898438,82467.304688</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>81970.398438,81765.609375,81598.101562,81464.757812,81337.921875,81173.289062</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>82227.937500,82100.906250,81983.406250,81856.929688,81782.296875,81658.437500</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3609,6 +3609,44 @@
       </c>
       <c r="F84" t="n">
         <v>82490.03125</v>
+      </c>
+      <c r="G84" t="n">
+        <v>82986.7421875</v>
+      </c>
+      <c r="H84" t="n">
+        <v>496.7109375</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.5985425194517611</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0.3599510698653284</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-10-11 05:28:30</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6</v>
+      </c>
+      <c r="F85" t="n">
+        <v>82901.625</v>
       </c>
     </row>
   </sheetData>
@@ -3622,7 +3660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M84"/>
+  <dimension ref="A1:M85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8721,6 +8759,24 @@
           <t>82666.835938,82648.687500,82644.046875,82577.320312,82590.945312,82490.031250</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>82800.687500,82974.351562,83004.609375,82910.640625,82732.093750,82986.742188</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>133.851562,325.664062,360.562500,333.320313,141.148438,496.710938</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>0.161655,0.392488,0.434389,0.402024,0.170609,0.598543</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>0.3599510698653284</v>
+      </c>
       <c r="K84" t="inlineStr">
         <is>
           <t>82652.382812,82782.132812,82624.257812,82615.773438,82620.898438,82467.304688</t>
@@ -8734,6 +8790,49 @@
       <c r="M84" t="inlineStr">
         <is>
           <t>82227.937500,82100.906250,81983.406250,81856.929688,81782.296875,81658.437500</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-10-11 05:28:30</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>82946.265625,82938.632812,82904.335938,82891.414062,82918.421875,82901.625000</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>82964.226562,83084.773438,82848.328125,82868.742188,82937.257812,82879.664062</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>82395.382812,82259.484375,82052.804688,81941.265625,81879.968750,81775.148438</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>82617.835938,82514.523438,82376.335938,82301.296875,82245.906250,82237.312500</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3647,6 +3647,44 @@
       </c>
       <c r="F85" t="n">
         <v>82901.625</v>
+      </c>
+      <c r="G85" t="n">
+        <v>83804.3203125</v>
+      </c>
+      <c r="H85" t="n">
+        <v>902.6953125</v>
+      </c>
+      <c r="I85" t="n">
+        <v>1.077146511222712</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0.7875847983973632</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-10-12 05:39:39</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6</v>
+      </c>
+      <c r="F86" t="n">
+        <v>83721.171875</v>
       </c>
     </row>
   </sheetData>
@@ -3660,7 +3698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M85"/>
+  <dimension ref="A1:M86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8820,6 +8858,24 @@
           <t>82946.265625,82938.632812,82904.335938,82891.414062,82918.421875,82901.625000</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>83074.468750,83815.710938,83574.953125,83680.593750,83504.710938,83804.320312</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>128.203125,877.078126,670.617187,789.179688,586.289062,902.695312</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>0.154323,1.046436,0.802414,0.943086,0.702103,1.077147</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>0.7875847983973632</v>
+      </c>
       <c r="K85" t="inlineStr">
         <is>
           <t>82964.226562,83084.773438,82848.328125,82868.742188,82937.257812,82879.664062</t>
@@ -8833,6 +8889,49 @@
       <c r="M85" t="inlineStr">
         <is>
           <t>82617.835938,82514.523438,82376.335938,82301.296875,82245.906250,82237.312500</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-10-12 05:39:39</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>83742.601562,83727.960938,83680.679688,83687.859375,83699.585938,83721.171875</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>83736.875000,83729.257812,83669.390625,83635.757812,83704.257812,83707.289062</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>83125.375000,82974.500000,82793.187500,82695.546875,82658.445312,82582.468750</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>83358.734375,83257.343750,83111.554688,83097.023438,83018.828125,83031.781250</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3685,6 +3685,44 @@
       </c>
       <c r="F86" t="n">
         <v>83721.171875</v>
+      </c>
+      <c r="G86" t="n">
+        <v>83635.796875</v>
+      </c>
+      <c r="H86" t="n">
+        <v>85.375</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.1020794960889766</v>
+      </c>
+      <c r="J86" t="n">
+        <v>1.000344363425782</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-10-13 06:35:53</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6</v>
+      </c>
+      <c r="F87" t="n">
+        <v>83610.53125</v>
       </c>
     </row>
   </sheetData>
@@ -3698,7 +3736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M86"/>
+  <dimension ref="A1:M87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8919,6 +8957,24 @@
           <t>83742.601562,83727.960938,83680.679688,83687.859375,83699.585938,83721.171875</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>83315.773438,82630.210938,82758.078125,81742.500000,83229.757812,83635.796875</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>426.828124,1097.750001,922.601563,1945.359375,469.828126,85.375000</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>0.512302,1.328509,1.114818,2.379863,0.564495,0.102079</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>1.000344363425782</v>
+      </c>
       <c r="K86" t="inlineStr">
         <is>
           <t>83736.875000,83729.257812,83669.390625,83635.757812,83704.257812,83707.289062</t>
@@ -8932,6 +8988,49 @@
       <c r="M86" t="inlineStr">
         <is>
           <t>83358.734375,83257.343750,83111.554688,83097.023438,83018.828125,83031.781250</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-10-13 06:35:53</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>83608.359375,83643.054688,83607.937500,83598.539062,83624.523438,83610.531250</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>83589.906250,83642.960938,83609.546875,83599.351562,83661.289062,83563.484375</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>82787.539062,82627.031250,82410.273438,82257.351562,82233.218750,82089.265625</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>83086.703125,82995.578125,82850.601562,82813.835938,82753.992188,82675.390625</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3723,6 +3723,44 @@
       </c>
       <c r="F87" t="n">
         <v>83610.53125</v>
+      </c>
+      <c r="G87" t="n">
+        <v>83780.2890625</v>
+      </c>
+      <c r="H87" t="n">
+        <v>169.7578125</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.2026226149367435</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0.347243935981984</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-10-14 04:36:32</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6</v>
+      </c>
+      <c r="F88" t="n">
+        <v>83710.2578125</v>
       </c>
     </row>
   </sheetData>
@@ -3736,7 +3774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M87"/>
+  <dimension ref="A1:M88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9018,6 +9056,24 @@
           <t>83608.359375,83643.054688,83607.937500,83598.539062,83624.523438,83610.531250</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>83250.078125,83337.531250,83205.437500,83101.992188,83626.703125,83780.289062</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>358.281250,305.523438,402.500000,496.546874,2.179687,169.757812</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>0.430367,0.366610,0.483742,0.597515,0.002606,0.202623</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>0.347243935981984</v>
+      </c>
       <c r="K87" t="inlineStr">
         <is>
           <t>83589.906250,83642.960938,83609.546875,83599.351562,83661.289062,83563.484375</t>
@@ -9031,6 +9087,49 @@
       <c r="M87" t="inlineStr">
         <is>
           <t>83086.703125,82995.578125,82850.601562,82813.835938,82753.992188,82675.390625</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-10-14 04:36:32</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>83711.203125,83754.664062,83654.265625,83586.000000,83742.382812,83710.257812</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>83739.062500,83645.953125,83701.281250,83603.046875,83681.234375,83509.289062</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>83035.335938,82805.484375,82466.406250,82215.796875,82322.539062,82145.460938</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>83283.867188,83222.335938,82977.703125,82838.679688,82885.304688,82811.437500</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J88"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3761,6 +3761,44 @@
       </c>
       <c r="F88" t="n">
         <v>83710.2578125</v>
+      </c>
+      <c r="G88" t="n">
+        <v>80966.6484375</v>
+      </c>
+      <c r="H88" t="n">
+        <v>2743.609375</v>
+      </c>
+      <c r="I88" t="n">
+        <v>3.388567302644192</v>
+      </c>
+      <c r="J88" t="n">
+        <v>2.487278529637006</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-10-15 04:19:07</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6</v>
+      </c>
+      <c r="F89" t="n">
+        <v>80384.484375</v>
       </c>
     </row>
   </sheetData>
@@ -3774,7 +3812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M88"/>
+  <dimension ref="A1:M89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9117,6 +9155,24 @@
           <t>83711.203125,83754.664062,83654.265625,83586.000000,83742.382812,83710.257812</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>83383.671875,81545.281250,81736.367188,81566.281250,80824.382812,80966.648438</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>327.531250,2209.382812,1917.898438,2019.718750,2917.999999,2743.609374</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>0.392800,2.709394,2.346444,2.476169,3.610297,3.388567</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>2.487278529637006</v>
+      </c>
       <c r="K88" t="inlineStr">
         <is>
           <t>83739.062500,83645.953125,83701.281250,83603.046875,83681.234375,83509.289062</t>
@@ -9130,6 +9186,49 @@
       <c r="M88" t="inlineStr">
         <is>
           <t>83283.867188,83222.335938,82977.703125,82838.679688,82885.304688,82811.437500</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-10-15 04:19:07</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>80793.328125,80679.171875,80609.765625,80501.710938,80588.648438,80384.484375</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>80751.156250,80604.195312,80449.742188,80569.296875,80779.406250,80406.242188</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>79586.773438,79082.921875,78786.437500,78412.453125,78236.703125,77771.843750</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>80046.523438,79783.109375,79572.710938,79312.671875,79204.406250,78835.109375</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J89"/>
+  <dimension ref="A1:J90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3799,6 +3799,44 @@
       </c>
       <c r="F89" t="n">
         <v>80384.484375</v>
+      </c>
+      <c r="G89" t="n">
+        <v>81952.0234375</v>
+      </c>
+      <c r="H89" t="n">
+        <v>1567.5390625</v>
+      </c>
+      <c r="I89" t="n">
+        <v>1.912752116115193</v>
+      </c>
+      <c r="J89" t="n">
+        <v>1.628545025888274</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:14:41</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>6</v>
+      </c>
+      <c r="F90" t="n">
+        <v>81855.046875</v>
       </c>
     </row>
   </sheetData>
@@ -3812,7 +3850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M89"/>
+  <dimension ref="A1:M90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9216,6 +9254,24 @@
           <t>80793.328125,80679.171875,80609.765625,80501.710938,80588.648438,80384.484375</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>80868.398438,82338.953125,82299.250000,82116.203125,82008.156250,81952.023438</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>75.070312,1659.781250,1689.484375,1614.492187,1419.507812,1567.539062</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>0.092830,2.015791,2.052855,1.966107,1.730935,1.912752</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>1.628545025888274</v>
+      </c>
       <c r="K89" t="inlineStr">
         <is>
           <t>80751.156250,80604.195312,80449.742188,80569.296875,80779.406250,80406.242188</t>
@@ -9229,6 +9285,49 @@
       <c r="M89" t="inlineStr">
         <is>
           <t>80046.523438,79783.109375,79572.710938,79312.671875,79204.406250,78835.109375</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:14:41</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>6</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>81941.515625,81943.500000,81887.328125,81852.257812,81842.101562,81855.046875</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>81924.093750,81927.437500,81854.296875,81926.265625,81858.468750,81850.843750</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>81037.140625,80867.093750,80686.351562,80523.117188,80461.890625,80355.562500</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>81413.507812,81334.453125,81177.710938,81080.210938,80959.093750,80945.187500</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J90"/>
+  <dimension ref="A1:J91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3837,6 +3837,44 @@
       </c>
       <c r="F90" t="n">
         <v>81855.046875</v>
+      </c>
+      <c r="G90" t="n">
+        <v>81411.8671875</v>
+      </c>
+      <c r="H90" t="n">
+        <v>443.1796875</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.5443674280056875</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0.5916725059664538</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-10-17 04:04:49</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6</v>
+      </c>
+      <c r="F91" t="n">
+        <v>81550.0703125</v>
       </c>
     </row>
   </sheetData>
@@ -3850,7 +3888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M90"/>
+  <dimension ref="A1:M91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9315,6 +9353,24 @@
           <t>81941.515625,81943.500000,81887.328125,81852.257812,81842.101562,81855.046875</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>82528.976562,81240.078125,81467.500000,81500.039062,81450.742188,81411.867188</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>587.460938,703.421875,419.828125,352.218749,391.359374,443.179688</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>0.711824,0.865856,0.515332,0.432170,0.480486,0.544367</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>0.5916725059664538</v>
+      </c>
       <c r="K90" t="inlineStr">
         <is>
           <t>81924.093750,81927.437500,81854.296875,81926.265625,81858.468750,81850.843750</t>
@@ -9328,6 +9384,49 @@
       <c r="M90" t="inlineStr">
         <is>
           <t>81413.507812,81334.453125,81177.710938,81080.210938,80959.093750,80945.187500</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-10-17 04:04:49</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>81405.023438,81465.296875,81494.835938,81511.281250,81539.242188,81550.070312</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>81407.515625,81537.093750,81499.648438,81547.921875,81545.953125,81625.765625</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>80594.304688,80510.460938,80427.054688,80362.812500,80318.914062,80244.343750</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>80917.695312,80898.382812,80838.101562,80805.546875,80750.445312,80736.093750</t>
         </is>
       </c>
     </row>
